--- a/time_tracking_forms/028_shared_living_clock_in_and_out_form--time_tracking_forms.xlsx
+++ b/time_tracking_forms/028_shared_living_clock_in_and_out_form--time_tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Driver ID</t>
+          <t>Clock In Form Driver Id</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Clock In Form Status</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>clock_out_form_status</t>
+          <t>clock_out_form_status_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Clock Out Form Status 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Clock Out Form Note</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Shift ID</t>
+          <t>Clock Out Form Shift Id</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>clock_in_form_shift_id</t>
+          <t>clock_in_form_shift_id_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Shift ID</t>
+          <t>Clock In Form Shift Id 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -986,7 +986,7 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1181,7 +1181,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>clock_out_form_status_choices</t>
+          <t>clock_out_form_status_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1198,7 +1198,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>clock_out_form_status_choices</t>
+          <t>clock_out_form_status_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
